--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.03556587168419739</v>
       </c>
       <c r="C2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>26718810</v>
+        <v>4072488</v>
       </c>
       <c r="L2" t="n">
-        <v>15865302</v>
+        <v>2186102</v>
       </c>
       <c r="M2" t="n">
-        <v>4112077</v>
+        <v>521233</v>
       </c>
       <c r="N2" t="n">
-        <v>238632</v>
+        <v>23707</v>
       </c>
       <c r="O2" t="n">
-        <v>2451560</v>
+        <v>327292</v>
       </c>
       <c r="P2" t="n">
-        <v>985391</v>
+        <v>139246</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999580383300781</v>
+        <v>0.9999029636383057</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9079326987266541</v>
+        <v>0.8302797079086304</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8098223805427551</v>
+        <v>0.6690024733543396</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7474403977394104</v>
+        <v>0.5701065063476562</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5830930471420288</v>
+        <v>0.3499188125133514</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8015597462654114</v>
+        <v>0.6421998143196106</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8526747226715088</v>
+        <v>0.7226163148880005</v>
       </c>
       <c r="X2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>25940546</v>
+        <v>3984507</v>
       </c>
       <c r="AG2" t="n">
-        <v>14584543</v>
+        <v>2036603</v>
       </c>
       <c r="AH2" t="n">
-        <v>3710241</v>
+        <v>481192</v>
       </c>
       <c r="AI2" t="n">
-        <v>219450</v>
+        <v>22644</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2245041</v>
+        <v>303181</v>
       </c>
       <c r="AK2" t="n">
-        <v>927068</v>
+        <v>131107</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.875588059425354</v>
+        <v>0.8069498538970947</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7586426734924316</v>
+        <v>0.6356266140937805</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6677120923995972</v>
+        <v>0.5195851922035217</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4138473272323608</v>
+        <v>0.2562175989151001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7364836931228638</v>
+        <v>0.5967495441436768</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7994874119758606</v>
+        <v>0.6783864498138428</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.009690508015213642</v>
       </c>
       <c r="C3" t="n">
-        <v>355</v>
+        <v>165</v>
       </c>
       <c r="D3" t="n">
-        <v>26718810</v>
+        <v>4072488</v>
       </c>
       <c r="E3" t="n">
-        <v>2623421</v>
+        <v>770995</v>
       </c>
       <c r="F3" t="n">
-        <v>94266</v>
+        <v>33472</v>
       </c>
       <c r="G3" t="n">
-        <v>17172</v>
+        <v>4904</v>
       </c>
       <c r="H3" t="n">
-        <v>3762</v>
+        <v>2040</v>
       </c>
       <c r="I3" t="n">
-        <v>461</v>
+        <v>187</v>
       </c>
       <c r="J3" t="n">
-        <v>59144203</v>
+        <v>9857025</v>
       </c>
       <c r="K3" t="n">
-        <v>64254779</v>
+        <v>10353678</v>
       </c>
       <c r="L3" t="n">
-        <v>73334688</v>
+        <v>11740374</v>
       </c>
       <c r="M3" t="n">
-        <v>89453763</v>
+        <v>14744426</v>
       </c>
       <c r="N3" t="n">
-        <v>95719855</v>
+        <v>15937520</v>
       </c>
       <c r="O3" t="n">
-        <v>92760997</v>
+        <v>15378308</v>
       </c>
       <c r="P3" t="n">
-        <v>95092119</v>
+        <v>15823509</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9070060849189758</v>
+        <v>0.8337998986244202</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8194072246551514</v>
+        <v>0.672973096370697</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7370411157608032</v>
+        <v>0.5587029457092285</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4486196339130402</v>
+        <v>0.2668595314025879</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8026123046875</v>
+        <v>0.6420738101005554</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8494566679000854</v>
+        <v>0.7198407649993896</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>25940546</v>
+        <v>3984507</v>
       </c>
       <c r="Z3" t="n">
-        <v>3272259</v>
+        <v>830301</v>
       </c>
       <c r="AA3" t="n">
-        <v>162855</v>
+        <v>49557</v>
       </c>
       <c r="AB3" t="n">
-        <v>75253</v>
+        <v>16367</v>
       </c>
       <c r="AC3" t="n">
-        <v>6513</v>
+        <v>3146</v>
       </c>
       <c r="AD3" t="n">
-        <v>821</v>
+        <v>373</v>
       </c>
       <c r="AE3" t="n">
-        <v>59145768</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>63278271</v>
+        <v>10232918</v>
       </c>
       <c r="AG3" t="n">
-        <v>72420495</v>
+        <v>11654492</v>
       </c>
       <c r="AH3" t="n">
-        <v>88996824</v>
+        <v>14692550</v>
       </c>
       <c r="AI3" t="n">
-        <v>95579657</v>
+        <v>15915829</v>
       </c>
       <c r="AJ3" t="n">
-        <v>92564641</v>
+        <v>15355785</v>
       </c>
       <c r="AK3" t="n">
-        <v>95029865</v>
+        <v>15814804</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8805868625640869</v>
+        <v>0.8157867193222046</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7532588839530945</v>
+        <v>0.6269510984420776</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.665016770362854</v>
+        <v>0.5157835483551025</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4125581681728363</v>
+        <v>0.2548937797546387</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7350003719329834</v>
+        <v>0.5947734117507935</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7991793155670166</v>
+        <v>0.6777657270431519</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07949827213633415</v>
       </c>
       <c r="C4" t="n">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>2564421</v>
+        <v>786124</v>
       </c>
       <c r="E4" t="n">
-        <v>15865302</v>
+        <v>2186102</v>
       </c>
       <c r="F4" t="n">
-        <v>825832</v>
+        <v>234166</v>
       </c>
       <c r="G4" t="n">
-        <v>28462</v>
+        <v>9125</v>
       </c>
       <c r="H4" t="n">
-        <v>70601</v>
+        <v>29343</v>
       </c>
       <c r="I4" t="n">
-        <v>7168</v>
+        <v>3498</v>
       </c>
       <c r="J4" t="n">
-        <v>1565</v>
+        <v>603</v>
       </c>
       <c r="K4" t="n">
-        <v>2709374</v>
+        <v>832471</v>
       </c>
       <c r="L4" t="n">
-        <v>3725786</v>
+        <v>1081602</v>
       </c>
       <c r="M4" t="n">
-        <v>1389468</v>
+        <v>393040</v>
       </c>
       <c r="N4" t="n">
-        <v>170620</v>
+        <v>44043</v>
       </c>
       <c r="O4" t="n">
-        <v>606927</v>
+        <v>182350</v>
       </c>
       <c r="P4" t="n">
-        <v>170256</v>
+        <v>53451</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999790191650391</v>
+        <v>0.9999514818191528</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9074691534042358</v>
+        <v>0.8320360779762268</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8145866990089417</v>
+        <v>0.6709819436073303</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7422043085098267</v>
+        <v>0.5643471479415894</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5070927143096924</v>
+        <v>0.3027965128421783</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8020856976509094</v>
+        <v>0.642136812210083</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8510626554489136</v>
+        <v>0.7212258577346802</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>3477910</v>
+        <v>892487</v>
       </c>
       <c r="Z4" t="n">
-        <v>14584543</v>
+        <v>2036603</v>
       </c>
       <c r="AA4" t="n">
-        <v>1106884</v>
+        <v>259401</v>
       </c>
       <c r="AB4" t="n">
-        <v>72388</v>
+        <v>16989</v>
       </c>
       <c r="AC4" t="n">
-        <v>107852</v>
+        <v>37896</v>
       </c>
       <c r="AD4" t="n">
-        <v>12349</v>
+        <v>5048</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3685882</v>
+        <v>953231</v>
       </c>
       <c r="AG4" t="n">
-        <v>4639979</v>
+        <v>1167484</v>
       </c>
       <c r="AH4" t="n">
-        <v>1846407</v>
+        <v>444916</v>
       </c>
       <c r="AI4" t="n">
-        <v>310818</v>
+        <v>65734</v>
       </c>
       <c r="AJ4" t="n">
-        <v>803283</v>
+        <v>204873</v>
       </c>
       <c r="AK4" t="n">
-        <v>232510</v>
+        <v>62156</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8780803084373474</v>
+        <v>0.8113442063331604</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7559411525726318</v>
+        <v>0.631259024143219</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6663616895675659</v>
+        <v>0.517677366733551</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4132017195224762</v>
+        <v>0.2555539906024933</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7357413172721863</v>
+        <v>0.5957598090171814</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7993333339691162</v>
+        <v>0.678075909614563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>281</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>91224</v>
+        <v>31742</v>
       </c>
       <c r="E5" t="n">
-        <v>951080</v>
+        <v>257584</v>
       </c>
       <c r="F5" t="n">
-        <v>4112077</v>
+        <v>521233</v>
       </c>
       <c r="G5" t="n">
-        <v>68122</v>
+        <v>16461</v>
       </c>
       <c r="H5" t="n">
-        <v>328357</v>
+        <v>94451</v>
       </c>
       <c r="I5" t="n">
-        <v>28028</v>
+        <v>11341</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2739437</v>
+        <v>811763</v>
       </c>
       <c r="L5" t="n">
-        <v>3496624</v>
+        <v>1062322</v>
       </c>
       <c r="M5" t="n">
-        <v>1467092</v>
+        <v>411701</v>
       </c>
       <c r="N5" t="n">
-        <v>293293</v>
+        <v>65130</v>
       </c>
       <c r="O5" t="n">
-        <v>602916</v>
+        <v>182450</v>
       </c>
       <c r="P5" t="n">
-        <v>174634</v>
+        <v>54194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999837875366211</v>
+        <v>0.9999624490737915</v>
       </c>
       <c r="R5" t="n">
-        <v>0.943490207195282</v>
+        <v>0.8976855874061584</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9250961542129517</v>
+        <v>0.86659175157547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9703745245933533</v>
+        <v>0.9499239921569824</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9951887130737305</v>
+        <v>0.9932065606117249</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9874526858329773</v>
+        <v>0.9772998690605164</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9964231252670288</v>
+        <v>0.9933016896247864</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>135402</v>
+        <v>43217</v>
       </c>
       <c r="Z5" t="n">
-        <v>1169428</v>
+        <v>272950</v>
       </c>
       <c r="AA5" t="n">
-        <v>3710241</v>
+        <v>481192</v>
       </c>
       <c r="AB5" t="n">
-        <v>91461</v>
+        <v>18183</v>
       </c>
       <c r="AC5" t="n">
-        <v>430141</v>
+        <v>102950</v>
       </c>
       <c r="AD5" t="n">
-        <v>42496</v>
+        <v>14442</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>3517701</v>
+        <v>899744</v>
       </c>
       <c r="AG5" t="n">
-        <v>4777383</v>
+        <v>1211821</v>
       </c>
       <c r="AH5" t="n">
-        <v>1868928</v>
+        <v>451742</v>
       </c>
       <c r="AI5" t="n">
-        <v>312475</v>
+        <v>66193</v>
       </c>
       <c r="AJ5" t="n">
-        <v>809435</v>
+        <v>206561</v>
       </c>
       <c r="AK5" t="n">
-        <v>232957</v>
+        <v>62333</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9252914190292358</v>
+        <v>0.8846964240074158</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9023322463035583</v>
+        <v>0.8519448637962341</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9614681601524353</v>
+        <v>0.9442043900489807</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9935358166694641</v>
+        <v>0.9917907118797302</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9832744598388672</v>
+        <v>0.9743980169296265</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9951726198196411</v>
+        <v>0.9922535419464111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>554</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>51868</v>
+        <v>13284</v>
       </c>
       <c r="E6" t="n">
-        <v>74297</v>
+        <v>18724</v>
       </c>
       <c r="F6" t="n">
-        <v>107403</v>
+        <v>18721</v>
       </c>
       <c r="G6" t="n">
-        <v>238632</v>
+        <v>23707</v>
       </c>
       <c r="H6" t="n">
-        <v>52457</v>
+        <v>12124</v>
       </c>
       <c r="I6" t="n">
-        <v>6714</v>
+        <v>2093</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>67653</v>
+        <v>14535</v>
       </c>
       <c r="Z6" t="n">
-        <v>75733</v>
+        <v>18407</v>
       </c>
       <c r="AA6" t="n">
-        <v>97813</v>
+        <v>18577</v>
       </c>
       <c r="AB6" t="n">
-        <v>219450</v>
+        <v>22644</v>
       </c>
       <c r="AC6" t="n">
-        <v>62527</v>
+        <v>12340</v>
       </c>
       <c r="AD6" t="n">
-        <v>8749</v>
+        <v>2334</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>1656</v>
+        <v>1259</v>
       </c>
       <c r="E7" t="n">
-        <v>72647</v>
+        <v>32066</v>
       </c>
       <c r="F7" t="n">
-        <v>347653</v>
+        <v>100649</v>
       </c>
       <c r="G7" t="n">
-        <v>52958</v>
+        <v>12104</v>
       </c>
       <c r="H7" t="n">
-        <v>2451560</v>
+        <v>327292</v>
       </c>
       <c r="I7" t="n">
-        <v>127885</v>
+        <v>36332</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>4586</v>
+        <v>2906</v>
       </c>
       <c r="Z7" t="n">
-        <v>114737</v>
+        <v>42232</v>
       </c>
       <c r="AA7" t="n">
-        <v>456308</v>
+        <v>109140</v>
       </c>
       <c r="AB7" t="n">
-        <v>65709</v>
+        <v>12324</v>
       </c>
       <c r="AC7" t="n">
-        <v>2245041</v>
+        <v>303181</v>
       </c>
       <c r="AD7" t="n">
-        <v>168095</v>
+        <v>39959</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>205</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>4341</v>
+        <v>2233</v>
       </c>
       <c r="F8" t="n">
-        <v>14314</v>
+        <v>6032</v>
       </c>
       <c r="G8" t="n">
-        <v>3906</v>
+        <v>1449</v>
       </c>
       <c r="H8" t="n">
-        <v>151750</v>
+        <v>44392</v>
       </c>
       <c r="I8" t="n">
-        <v>985391</v>
+        <v>139246</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="Z8" t="n">
-        <v>7822</v>
+        <v>3594</v>
       </c>
       <c r="AA8" t="n">
-        <v>22547</v>
+        <v>8241</v>
       </c>
       <c r="AB8" t="n">
-        <v>6007</v>
+        <v>1871</v>
       </c>
       <c r="AC8" t="n">
-        <v>196250</v>
+        <v>48541</v>
       </c>
       <c r="AD8" t="n">
-        <v>927068</v>
+        <v>131107</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
